--- a/python_engine/data/output/0829 스케줄링결과.xlsx
+++ b/python_engine/data/output/0829 스케줄링결과.xlsx
@@ -709,7 +709,7 @@
         <v>1300</v>
       </c>
       <c r="J3" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
